--- a/public/finance-setup-template.xlsx
+++ b/public/finance-setup-template.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:A14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,646 +424,595 @@
         <v>You can delete the example rows; they are just there to show the shape.</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Allowed values for enum columns (case-insensitive at import):</v>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Each sheet has its own KEY at the top — that block is ignored by the importer, it is for your reference only.</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Cross-references that must match exactly (by name):</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Accounts.type</v>
-      </c>
-      <c r="B9" t="str">
-        <v>checking, hysa, roth_ira, brokerage, cash, other</v>
+        <v xml:space="preserve">  Income.depositAccount → must equal an Accounts.name in this file</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Liabilities.type</v>
-      </c>
-      <c r="B10" t="str">
-        <v>credit_card, student_loan, auto_loan, personal_loan, other</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Income.sourceType</v>
-      </c>
-      <c r="B11" t="str">
-        <v>paycheck, bonus, gift, reimbursement, side_income, other</v>
+        <v xml:space="preserve">  Tiers.targetAccount    → must equal an Accounts.name in this file</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Expenses.category</v>
-      </c>
-      <c r="B12" t="str">
-        <v>housing, food, transportation, insurance, debt, subscriptions, entertainment, health, misc</v>
+        <v>Booleans accept: true / false / yes / no / 1 / 0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Cadence (Income &amp; Expenses)</v>
-      </c>
-      <c r="B13" t="str">
-        <v>weekly, biweekly, semimonthly, monthly, quarterly, annual, irregular</v>
+        <v>Dates accept: YYYY-MM-DD or any standard format Excel exports</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Expenses.paymentMethod</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Bank Transfer, Credit Card, Cash, Autopay, Other</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Tiers.capType</v>
-      </c>
-      <c r="B15" t="str">
-        <v>fixed, dynamic, unlimited</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>Tiers.resetCadence</v>
-      </c>
-      <c r="B16" t="str">
-        <v>none, annual, monthly, per_statement</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>Booleans (isActive / isRevolving / openedYet)</v>
-      </c>
-      <c r="B17" t="str">
-        <v>true / false (or yes/no, 1/0)</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Cross-references that must match exactly (by name):</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v xml:space="preserve">  Income.depositAccount → must equal an Accounts.name in this file</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v xml:space="preserve">  Tiers.targetAccount    → must equal an Accounts.name in this file</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>Date columns (Liabilities.dueDate) accept YYYY-MM-DD or any standard format Excel exports.</v>
+        <v>Numbers accept: $1,200.00 (commas and $ are stripped)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A14"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>name*</v>
-      </c>
-      <c r="B1" t="str">
-        <v>type*</v>
-      </c>
-      <c r="C1" t="str">
-        <v>balance*</v>
-      </c>
-      <c r="D1" t="str">
-        <v>institution</v>
-      </c>
-      <c r="E1" t="str">
-        <v>openedYet</v>
-      </c>
-      <c r="F1" t="str">
-        <v>sortOrder</v>
-      </c>
-      <c r="G1" t="str">
-        <v>notes</v>
+        <v>KEY — fields that will fail validation if entered incorrectly:</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Chase Checking</v>
+        <v>type</v>
       </c>
       <c r="B2" t="str">
-        <v>checking</v>
-      </c>
-      <c r="C2">
-        <v>500</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Chase</v>
-      </c>
-      <c r="E2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Primary checking</v>
+        <v>one of: checking, hysa, roth_ira, brokerage, cash, other</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Ally HYSA</v>
+        <v>name</v>
       </c>
       <c r="B3" t="str">
-        <v>hysa</v>
-      </c>
-      <c r="C3">
-        <v>2000</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Ally</v>
-      </c>
-      <c r="E3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Emergency fund</v>
+        <v>required; must be unique within this sheet</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Fidelity Roth IRA</v>
+        <v>balance</v>
       </c>
       <c r="B4" t="str">
-        <v>roth_ira</v>
-      </c>
-      <c r="C4">
-        <v>1500</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Fidelity</v>
-      </c>
-      <c r="E4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-      <c r="G4" t="str">
-        <v/>
+        <v>number (e.g., 500 or 1,250.43)</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
+        <v>openedYet</v>
+      </c>
+      <c r="B5" t="str">
+        <v>true / false — defaults to true if blank</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>sortOrder</v>
+      </c>
+      <c r="B6" t="str">
+        <v>optional integer — display order on Payday &amp; Accounts</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>name*</v>
+      </c>
+      <c r="B8" t="str">
+        <v>type*</v>
+      </c>
+      <c r="C8" t="str">
+        <v>balance*</v>
+      </c>
+      <c r="D8" t="str">
+        <v>institution</v>
+      </c>
+      <c r="E8" t="str">
+        <v>openedYet</v>
+      </c>
+      <c r="F8" t="str">
+        <v>sortOrder</v>
+      </c>
+      <c r="G8" t="str">
+        <v>notes</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Chase Checking</v>
+      </c>
+      <c r="B9" t="str">
+        <v>checking</v>
+      </c>
+      <c r="C9">
+        <v>500</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Chase</v>
+      </c>
+      <c r="E9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Primary checking</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Ally HYSA</v>
+      </c>
+      <c r="B10" t="str">
+        <v>hysa</v>
+      </c>
+      <c r="C10">
+        <v>2000</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Ally</v>
+      </c>
+      <c r="E10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Emergency fund</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Fidelity Roth IRA</v>
+      </c>
+      <c r="B11" t="str">
+        <v>roth_ira</v>
+      </c>
+      <c r="C11">
+        <v>1500</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Fidelity</v>
+      </c>
+      <c r="E11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
         <v>Fidelity Brokerage</v>
       </c>
-      <c r="B5" t="str">
+      <c r="B12" t="str">
         <v>brokerage</v>
       </c>
-      <c r="C5">
+      <c r="C12">
         <v>5000</v>
       </c>
-      <c r="D5" t="str">
+      <c r="D12" t="str">
         <v>Fidelity</v>
       </c>
-      <c r="E5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F5">
+      <c r="E12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12">
         <v>3</v>
       </c>
-      <c r="G5" t="str">
+      <c r="G12" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G12"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>name*</v>
-      </c>
-      <c r="B1" t="str">
-        <v>type*</v>
-      </c>
-      <c r="C1" t="str">
-        <v>balance*</v>
-      </c>
-      <c r="D1" t="str">
-        <v>apr*</v>
-      </c>
-      <c r="E1" t="str">
-        <v>minimumPayment*</v>
-      </c>
-      <c r="F1" t="str">
-        <v>isRevolving*</v>
-      </c>
-      <c r="G1" t="str">
-        <v>isActive*</v>
-      </c>
-      <c r="H1" t="str">
-        <v>dueDate</v>
-      </c>
-      <c r="I1" t="str">
-        <v>notes</v>
+        <v>KEY — fields that will fail validation if entered incorrectly:</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Chase Sapphire CC</v>
+        <v>type</v>
       </c>
       <c r="B2" t="str">
-        <v>credit_card</v>
-      </c>
-      <c r="C2">
-        <v>450</v>
-      </c>
-      <c r="D2">
-        <v>0.22</v>
-      </c>
-      <c r="E2">
-        <v>30</v>
-      </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H2" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Paid in full each cycle</v>
+        <v>one of: credit_card, student_loan, auto_loan, personal_loan, other</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Federal Student Loan</v>
+        <v>apr</v>
       </c>
       <c r="B3" t="str">
-        <v>student_loan</v>
-      </c>
-      <c r="C3">
-        <v>18000</v>
-      </c>
-      <c r="D3">
-        <v>0.055</v>
-      </c>
-      <c r="E3">
-        <v>200</v>
-      </c>
-      <c r="F3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v/>
+        <v>decimal (0.22 = 22%)</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
+        <v>isRevolving</v>
+      </c>
+      <c r="B4" t="str">
+        <v>true / false — credit cards = true, installment loans = false</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>isActive</v>
+      </c>
+      <c r="B5" t="str">
+        <v>true / false — uncheck to exclude from totals</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>dueDate</v>
+      </c>
+      <c r="B6" t="str">
+        <v>optional, YYYY-MM-DD; drives the CC runway warning on Payday</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>name*</v>
+      </c>
+      <c r="B8" t="str">
+        <v>type*</v>
+      </c>
+      <c r="C8" t="str">
+        <v>balance*</v>
+      </c>
+      <c r="D8" t="str">
+        <v>apr*</v>
+      </c>
+      <c r="E8" t="str">
+        <v>minimumPayment*</v>
+      </c>
+      <c r="F8" t="str">
+        <v>isRevolving*</v>
+      </c>
+      <c r="G8" t="str">
+        <v>isActive*</v>
+      </c>
+      <c r="H8" t="str">
+        <v>dueDate</v>
+      </c>
+      <c r="I8" t="str">
+        <v>notes</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Chase Sapphire CC</v>
+      </c>
+      <c r="B9" t="str">
+        <v>credit_card</v>
+      </c>
+      <c r="C9">
+        <v>450</v>
+      </c>
+      <c r="D9">
+        <v>0.22</v>
+      </c>
+      <c r="E9">
+        <v>30</v>
+      </c>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Paid in full each cycle</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Federal Student Loan</v>
+      </c>
+      <c r="B10" t="str">
+        <v>student_loan</v>
+      </c>
+      <c r="C10">
+        <v>18000</v>
+      </c>
+      <c r="D10">
+        <v>0.055</v>
+      </c>
+      <c r="E10">
+        <v>200</v>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
         <v>Auto Loan</v>
       </c>
-      <c r="B4" t="str">
+      <c r="B11" t="str">
         <v>auto_loan</v>
       </c>
-      <c r="C4">
+      <c r="C11">
         <v>12000</v>
       </c>
-      <c r="D4">
+      <c r="D11">
         <v>0.065</v>
       </c>
-      <c r="E4">
+      <c r="E11">
         <v>250</v>
       </c>
-      <c r="F4" t="b">
+      <c r="F11" t="b">
         <v>0</v>
       </c>
-      <c r="G4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
+      <c r="G11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I11"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>name*</v>
-      </c>
-      <c r="B1" t="str">
-        <v>sourceType*</v>
-      </c>
-      <c r="C1" t="str">
-        <v>amount*</v>
-      </c>
-      <c r="D1" t="str">
-        <v>cadence*</v>
-      </c>
-      <c r="E1" t="str">
-        <v>depositAccount*</v>
-      </c>
-      <c r="F1" t="str">
-        <v>isActive*</v>
-      </c>
-      <c r="G1" t="str">
-        <v>notes</v>
+        <v>KEY — fields that will fail validation if entered incorrectly:</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Day Job Paycheck</v>
+        <v>sourceType</v>
       </c>
       <c r="B2" t="str">
-        <v>paycheck</v>
-      </c>
-      <c r="C2">
-        <v>2200</v>
-      </c>
-      <c r="D2" t="str">
-        <v>biweekly</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Chase Checking</v>
-      </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G2" t="str">
-        <v>26 paydays/year</v>
+        <v>one of: paycheck, bonus, gift, reimbursement, side_income, other</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>cadence</v>
+      </c>
+      <c r="B3" t="str">
+        <v>one of: weekly, biweekly, semimonthly, monthly, quarterly, annual, irregular</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>depositAccount</v>
+      </c>
+      <c r="B4" t="str">
+        <v>must match an Accounts.name in the Accounts sheet of this file</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>amount</v>
+      </c>
+      <c r="B5" t="str">
+        <v>number — net per period for paychecks, total per event for irregular sources</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>name*</v>
+      </c>
+      <c r="B7" t="str">
+        <v>sourceType*</v>
+      </c>
+      <c r="C7" t="str">
+        <v>amount*</v>
+      </c>
+      <c r="D7" t="str">
+        <v>cadence*</v>
+      </c>
+      <c r="E7" t="str">
+        <v>depositAccount*</v>
+      </c>
+      <c r="F7" t="str">
+        <v>isActive*</v>
+      </c>
+      <c r="G7" t="str">
+        <v>notes</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Day Job Paycheck</v>
+      </c>
+      <c r="B8" t="str">
+        <v>paycheck</v>
+      </c>
+      <c r="C8">
+        <v>2200</v>
+      </c>
+      <c r="D8" t="str">
+        <v>biweekly</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Chase Checking</v>
+      </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" t="str">
+        <v>26 paydays/year</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
         <v>Freelance</v>
       </c>
-      <c r="B3" t="str">
+      <c r="B9" t="str">
         <v>side_income</v>
       </c>
-      <c r="C3">
+      <c r="C9">
         <v>500</v>
       </c>
-      <c r="D3" t="str">
+      <c r="D9" t="str">
         <v>irregular</v>
       </c>
-      <c r="E3" t="str">
+      <c r="E9" t="str">
         <v>Chase Checking</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3" t="str">
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" t="str">
         <v>Logged per gig</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G9"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>name*</v>
-      </c>
-      <c r="B1" t="str">
-        <v>category*</v>
-      </c>
-      <c r="C1" t="str">
-        <v>amount*</v>
-      </c>
-      <c r="D1" t="str">
-        <v>cadence*</v>
-      </c>
-      <c r="E1" t="str">
-        <v>paymentMethod*</v>
-      </c>
-      <c r="F1" t="str">
-        <v>isActive*</v>
-      </c>
-      <c r="G1" t="str">
-        <v>notes</v>
+        <v>KEY — fields that will fail validation if entered incorrectly:</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Rent</v>
+        <v>category</v>
       </c>
       <c r="B2" t="str">
-        <v>housing</v>
-      </c>
-      <c r="C2">
-        <v>1400</v>
-      </c>
-      <c r="D2" t="str">
-        <v>monthly</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Bank Transfer</v>
-      </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G2" t="str">
-        <v/>
+        <v>one of: housing, food, transportation, insurance, debt, subscriptions, entertainment, health, misc</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Car Insurance</v>
+        <v>cadence</v>
       </c>
       <c r="B3" t="str">
-        <v>insurance</v>
-      </c>
-      <c r="C3">
-        <v>150</v>
-      </c>
-      <c r="D3" t="str">
-        <v>monthly</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Bank Transfer</v>
-      </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
+        <v>one of: weekly, biweekly, semimonthly, monthly, quarterly, annual, irregular</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Student Loan Payment</v>
+        <v>paymentMethod</v>
       </c>
       <c r="B4" t="str">
-        <v>debt</v>
-      </c>
-      <c r="C4">
-        <v>200</v>
-      </c>
-      <c r="D4" t="str">
-        <v>monthly</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Bank Transfer</v>
-      </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G4" t="str">
-        <v/>
+        <v>one of: Bank Transfer, Credit Card, Cash, Autopay, Other (case-sensitive)</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Auto Loan Payment</v>
+        <v/>
       </c>
       <c r="B5" t="str">
-        <v>debt</v>
-      </c>
-      <c r="C5">
-        <v>250</v>
-      </c>
-      <c r="D5" t="str">
-        <v>monthly</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Bank Transfer</v>
-      </c>
-      <c r="F5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5" t="str">
-        <v/>
+        <v xml:space="preserve">  ↳ Bank Transfer expenses reserve cash in checking each paycheck</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Groceries</v>
+        <v/>
       </c>
       <c r="B6" t="str">
-        <v>food</v>
-      </c>
-      <c r="C6">
-        <v>400</v>
-      </c>
-      <c r="D6" t="str">
-        <v>monthly</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Credit Card</v>
-      </c>
-      <c r="F6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Gas</v>
-      </c>
-      <c r="B7" t="str">
-        <v>transportation</v>
-      </c>
-      <c r="C7">
-        <v>160</v>
-      </c>
-      <c r="D7" t="str">
-        <v>monthly</v>
-      </c>
-      <c r="E7" t="str">
-        <v>Credit Card</v>
-      </c>
-      <c r="F7" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" t="str">
-        <v/>
+        <v xml:space="preserve">  ↳ Credit Card expenses grow your CC balance instead</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Utilities</v>
+        <v>name*</v>
       </c>
       <c r="B8" t="str">
-        <v>housing</v>
-      </c>
-      <c r="C8">
-        <v>120</v>
+        <v>category*</v>
+      </c>
+      <c r="C8" t="str">
+        <v>amount*</v>
       </c>
       <c r="D8" t="str">
-        <v>monthly</v>
+        <v>cadence*</v>
       </c>
       <c r="E8" t="str">
-        <v>Credit Card</v>
-      </c>
-      <c r="F8" t="b">
-        <v>1</v>
+        <v>paymentMethod*</v>
+      </c>
+      <c r="F8" t="str">
+        <v>isActive*</v>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>notes</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Netflix</v>
+        <v>Rent</v>
       </c>
       <c r="B9" t="str">
-        <v>subscriptions</v>
+        <v>housing</v>
       </c>
       <c r="C9">
-        <v>15</v>
+        <v>1400</v>
       </c>
       <c r="D9" t="str">
         <v>monthly</v>
       </c>
       <c r="E9" t="str">
-        <v>Credit Card</v>
+        <v>Bank Transfer</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -1074,171 +1023,385 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Gym</v>
+        <v>Car Insurance</v>
       </c>
       <c r="B10" t="str">
-        <v>health</v>
+        <v>insurance</v>
       </c>
       <c r="C10">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="D10" t="str">
         <v>monthly</v>
       </c>
       <c r="E10" t="str">
+        <v>Bank Transfer</v>
+      </c>
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Student Loan Payment</v>
+      </c>
+      <c r="B11" t="str">
+        <v>debt</v>
+      </c>
+      <c r="C11">
+        <v>200</v>
+      </c>
+      <c r="D11" t="str">
+        <v>monthly</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Bank Transfer</v>
+      </c>
+      <c r="F11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Auto Loan Payment</v>
+      </c>
+      <c r="B12" t="str">
+        <v>debt</v>
+      </c>
+      <c r="C12">
+        <v>250</v>
+      </c>
+      <c r="D12" t="str">
+        <v>monthly</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Bank Transfer</v>
+      </c>
+      <c r="F12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Groceries</v>
+      </c>
+      <c r="B13" t="str">
+        <v>food</v>
+      </c>
+      <c r="C13">
+        <v>400</v>
+      </c>
+      <c r="D13" t="str">
+        <v>monthly</v>
+      </c>
+      <c r="E13" t="str">
         <v>Credit Card</v>
       </c>
-      <c r="F10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G10" t="str">
+      <c r="F13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Gas</v>
+      </c>
+      <c r="B14" t="str">
+        <v>transportation</v>
+      </c>
+      <c r="C14">
+        <v>160</v>
+      </c>
+      <c r="D14" t="str">
+        <v>monthly</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Credit Card</v>
+      </c>
+      <c r="F14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Utilities</v>
+      </c>
+      <c r="B15" t="str">
+        <v>housing</v>
+      </c>
+      <c r="C15">
+        <v>120</v>
+      </c>
+      <c r="D15" t="str">
+        <v>monthly</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Credit Card</v>
+      </c>
+      <c r="F15" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Netflix</v>
+      </c>
+      <c r="B16" t="str">
+        <v>subscriptions</v>
+      </c>
+      <c r="C16">
+        <v>15</v>
+      </c>
+      <c r="D16" t="str">
+        <v>monthly</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Credit Card</v>
+      </c>
+      <c r="F16" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Gym</v>
+      </c>
+      <c r="B17" t="str">
+        <v>health</v>
+      </c>
+      <c r="C17">
+        <v>40</v>
+      </c>
+      <c r="D17" t="str">
+        <v>monthly</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Credit Card</v>
+      </c>
+      <c r="F17" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G17"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>KEY — fields that will fail validation if entered incorrectly:</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>priority</v>
+      </c>
+      <c r="B2" t="str">
+        <v>integer — 0 fills first in the suggestion waterfall</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>capType</v>
+      </c>
+      <c r="B3" t="str">
+        <v>one of: fixed, dynamic, unlimited</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v/>
+      </c>
+      <c r="B4" t="str">
+        <v xml:space="preserve">  ↳ fixed = stop at "cap"; dynamic = computed at runtime; unlimited = catch-all</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>resetCadence</v>
+      </c>
+      <c r="B5" t="str">
+        <v>one of: none, annual, monthly, per_statement</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>targetAccount</v>
+      </c>
+      <c r="B6" t="str">
+        <v>must match an Accounts.name in the Accounts sheet of this file</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>cap</v>
+      </c>
+      <c r="B7" t="str">
+        <v>number — required, even when capType is unlimited (use 0)</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
         <v>priority*</v>
       </c>
-      <c r="B1" t="str">
+      <c r="B9" t="str">
         <v>name*</v>
       </c>
-      <c r="C1" t="str">
+      <c r="C9" t="str">
         <v>cap*</v>
       </c>
-      <c r="D1" t="str">
+      <c r="D9" t="str">
         <v>capType*</v>
       </c>
-      <c r="E1" t="str">
+      <c r="E9" t="str">
         <v>targetAccount*</v>
       </c>
-      <c r="F1" t="str">
+      <c r="F9" t="str">
         <v>resetCadence*</v>
       </c>
-      <c r="G1" t="str">
+      <c r="G9" t="str">
         <v>isActive*</v>
       </c>
-      <c r="H1" t="str">
+      <c r="H9" t="str">
         <v>notes</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2">
+    <row r="10">
+      <c r="A10">
         <v>0</v>
       </c>
-      <c r="B2" t="str">
+      <c r="B10" t="str">
         <v>CC Float Reserve</v>
       </c>
-      <c r="C2">
+      <c r="C10">
         <v>0</v>
       </c>
-      <c r="D2" t="str">
+      <c r="D10" t="str">
         <v>dynamic</v>
       </c>
-      <c r="E2" t="str">
+      <c r="E10" t="str">
         <v>Chase Checking</v>
       </c>
-      <c r="F2" t="str">
+      <c r="F10" t="str">
         <v>per_statement</v>
       </c>
-      <c r="G2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H2" t="str">
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" t="str">
         <v>Suggests CC balance + buffer in checking</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="str">
+    <row r="11">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11" t="str">
         <v>Emergency Fund</v>
       </c>
-      <c r="C3">
+      <c r="C11">
         <v>10000</v>
       </c>
-      <c r="D3" t="str">
+      <c r="D11" t="str">
         <v>fixed</v>
       </c>
-      <c r="E3" t="str">
+      <c r="E11" t="str">
         <v>Ally HYSA</v>
       </c>
-      <c r="F3" t="str">
+      <c r="F11" t="str">
         <v>none</v>
       </c>
-      <c r="G3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H3" t="str">
+      <c r="G11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" t="str">
         <v>Fill HYSA to $10,000</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4">
+    <row r="12">
+      <c r="A12">
         <v>2</v>
       </c>
-      <c r="B4" t="str">
+      <c r="B12" t="str">
         <v>Roth IRA</v>
       </c>
-      <c r="C4">
+      <c r="C12">
         <v>7000</v>
       </c>
-      <c r="D4" t="str">
+      <c r="D12" t="str">
         <v>fixed</v>
       </c>
-      <c r="E4" t="str">
+      <c r="E12" t="str">
         <v>Fidelity Roth IRA</v>
       </c>
-      <c r="F4" t="str">
+      <c r="F12" t="str">
         <v>annual</v>
       </c>
-      <c r="G4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H4" t="str">
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" t="str">
         <v>$7k annual cap</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5">
+    <row r="13">
+      <c r="A13">
         <v>3</v>
       </c>
-      <c r="B5" t="str">
+      <c r="B13" t="str">
         <v>Taxable Brokerage</v>
       </c>
-      <c r="C5">
+      <c r="C13">
         <v>0</v>
       </c>
-      <c r="D5" t="str">
+      <c r="D13" t="str">
         <v>unlimited</v>
       </c>
-      <c r="E5" t="str">
+      <c r="E13" t="str">
         <v>Fidelity Brokerage</v>
       </c>
-      <c r="F5" t="str">
+      <c r="F13" t="str">
         <v>none</v>
       </c>
-      <c r="G5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H5" t="str">
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" t="str">
         <v>Catches overflow</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H13"/>
   </ignoredErrors>
 </worksheet>
 </file>